--- a/metadata/metadata_Macaca_mulatta.xlsx
+++ b/metadata/metadata_Macaca_mulatta.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ms84/Research/postdoc/projects/PrimateSomatic/metadata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{328D04EC-6B83-364F-A41D-5C99C0DBBD12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C649A3CE-4E1B-7148-A346-BC042BC1EAAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="31780" yWindow="1800" windowWidth="28040" windowHeight="15040" xr2:uid="{DE405C7A-DE7E-F046-BCC9-57957EBF65EE}"/>
+    <workbookView xWindow="31800" yWindow="1840" windowWidth="28040" windowHeight="15040" xr2:uid="{DE405C7A-DE7E-F046-BCC9-57957EBF65EE}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -38,163 +38,163 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="53">
   <si>
+    <t>MQD0001d</t>
+  </si>
+  <si>
+    <t>MQD0001d_tds0001</t>
+  </si>
+  <si>
+    <t>Liver</t>
+  </si>
+  <si>
+    <t>MQD0001j</t>
+  </si>
+  <si>
+    <t>MQD0001j_tds0001</t>
+  </si>
+  <si>
+    <t>Bladder</t>
+  </si>
+  <si>
+    <t>MQD0002e</t>
+  </si>
+  <si>
+    <t>MQD0002e_tds0001</t>
+  </si>
+  <si>
+    <t>MQD0002f</t>
+  </si>
+  <si>
+    <t>MQD0002f_tds0001</t>
+  </si>
+  <si>
+    <t>Oesophagus</t>
+  </si>
+  <si>
+    <t>MQD0002h</t>
+  </si>
+  <si>
+    <t>MQD0002h_tds0001</t>
+  </si>
+  <si>
+    <t>Prostate</t>
+  </si>
+  <si>
+    <t>MQD0002l</t>
+  </si>
+  <si>
+    <t>MQD0002l_tds0001</t>
+  </si>
+  <si>
+    <t>MQD0003d</t>
+  </si>
+  <si>
+    <t>MQD0003d_tds0001</t>
+  </si>
+  <si>
+    <t>MQD0003e</t>
+  </si>
+  <si>
+    <t>MQD0003e_tds0001</t>
+  </si>
+  <si>
+    <t>MQD0003g</t>
+  </si>
+  <si>
+    <t>MQD0003g_tds0001</t>
+  </si>
+  <si>
+    <t>MQD0003j</t>
+  </si>
+  <si>
+    <t>MQD0003j_tds0001</t>
+  </si>
+  <si>
+    <t>MQD0004d</t>
+  </si>
+  <si>
+    <t>MQD0004d_tds0001</t>
+  </si>
+  <si>
+    <t>MQD0004e</t>
+  </si>
+  <si>
+    <t>MQD0004e_tds0002</t>
+  </si>
+  <si>
+    <t>MQD0004i</t>
+  </si>
+  <si>
+    <t>MQD0004i_tds0001</t>
+  </si>
+  <si>
+    <t>Skin</t>
+  </si>
+  <si>
+    <t>MQD0004k</t>
+  </si>
+  <si>
+    <t>MQD0004k_tds0002</t>
+  </si>
+  <si>
+    <t>MQD0006e</t>
+  </si>
+  <si>
+    <t>MQD0006e_tds0001</t>
+  </si>
+  <si>
+    <t>MQD0006f</t>
+  </si>
+  <si>
+    <t>MQD0006f_tds0001</t>
+  </si>
+  <si>
+    <t>MQD0006h</t>
+  </si>
+  <si>
+    <t>MQD0006h_tds0001</t>
+  </si>
+  <si>
+    <t>MQD0006l</t>
+  </si>
+  <si>
+    <t>MQD0006l_tds0001</t>
+  </si>
+  <si>
+    <t>Macaca_mulatta</t>
+  </si>
+  <si>
+    <t>MQD0001</t>
+  </si>
+  <si>
+    <t>MQD0002</t>
+  </si>
+  <si>
+    <t>MQD0003</t>
+  </si>
+  <si>
+    <t>MQD0004</t>
+  </si>
+  <si>
+    <t>MQD0006</t>
+  </si>
+  <si>
+    <t>species</t>
+  </si>
+  <si>
+    <t>individual</t>
+  </si>
+  <si>
+    <t>sample</t>
+  </si>
+  <si>
+    <t>sample_id</t>
+  </si>
+  <si>
     <t>age</t>
   </si>
   <si>
     <t>tissue</t>
-  </si>
-  <si>
-    <t>MQD0001d</t>
-  </si>
-  <si>
-    <t>MQD0001d_tds0001</t>
-  </si>
-  <si>
-    <t>Liver</t>
-  </si>
-  <si>
-    <t>MQD0001j</t>
-  </si>
-  <si>
-    <t>MQD0001j_tds0001</t>
-  </si>
-  <si>
-    <t>Bladder</t>
-  </si>
-  <si>
-    <t>MQD0002e</t>
-  </si>
-  <si>
-    <t>MQD0002e_tds0001</t>
-  </si>
-  <si>
-    <t>MQD0002f</t>
-  </si>
-  <si>
-    <t>MQD0002f_tds0001</t>
-  </si>
-  <si>
-    <t>Oesophagus</t>
-  </si>
-  <si>
-    <t>MQD0002h</t>
-  </si>
-  <si>
-    <t>MQD0002h_tds0001</t>
-  </si>
-  <si>
-    <t>Prostate</t>
-  </si>
-  <si>
-    <t>MQD0002l</t>
-  </si>
-  <si>
-    <t>MQD0002l_tds0001</t>
-  </si>
-  <si>
-    <t>MQD0003d</t>
-  </si>
-  <si>
-    <t>MQD0003d_tds0001</t>
-  </si>
-  <si>
-    <t>MQD0003e</t>
-  </si>
-  <si>
-    <t>MQD0003e_tds0001</t>
-  </si>
-  <si>
-    <t>MQD0003g</t>
-  </si>
-  <si>
-    <t>MQD0003g_tds0001</t>
-  </si>
-  <si>
-    <t>MQD0003j</t>
-  </si>
-  <si>
-    <t>MQD0003j_tds0001</t>
-  </si>
-  <si>
-    <t>MQD0004d</t>
-  </si>
-  <si>
-    <t>MQD0004d_tds0001</t>
-  </si>
-  <si>
-    <t>MQD0004e</t>
-  </si>
-  <si>
-    <t>MQD0004e_tds0002</t>
-  </si>
-  <si>
-    <t>MQD0004i</t>
-  </si>
-  <si>
-    <t>MQD0004i_tds0001</t>
-  </si>
-  <si>
-    <t>Skin</t>
-  </si>
-  <si>
-    <t>MQD0004k</t>
-  </si>
-  <si>
-    <t>MQD0004k_tds0002</t>
-  </si>
-  <si>
-    <t>MQD0006e</t>
-  </si>
-  <si>
-    <t>MQD0006e_tds0001</t>
-  </si>
-  <si>
-    <t>MQD0006f</t>
-  </si>
-  <si>
-    <t>MQD0006f_tds0001</t>
-  </si>
-  <si>
-    <t>MQD0006h</t>
-  </si>
-  <si>
-    <t>MQD0006h_tds0001</t>
-  </si>
-  <si>
-    <t>MQD0006l</t>
-  </si>
-  <si>
-    <t>MQD0006l_tds0001</t>
-  </si>
-  <si>
-    <t>species</t>
-  </si>
-  <si>
-    <t>Macaca_mulatta</t>
-  </si>
-  <si>
-    <t>sample_id</t>
-  </si>
-  <si>
-    <t>sample</t>
-  </si>
-  <si>
-    <t>individual</t>
-  </si>
-  <si>
-    <t>MQD0001</t>
-  </si>
-  <si>
-    <t>MQD0002</t>
-  </si>
-  <si>
-    <t>MQD0003</t>
-  </si>
-  <si>
-    <t>MQD0004</t>
-  </si>
-  <si>
-    <t>MQD0006</t>
   </si>
 </sst>
 </file>
@@ -584,382 +584,382 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="B1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>1</v>
+        <v>52</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B2" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E2" s="1">
         <v>15.37</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B3" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E3" s="1">
         <v>15.37</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B4" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E4" s="1">
         <v>5.41</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B5" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E5" s="1">
         <v>5.41</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B6" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E6" s="1">
         <v>5.41</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B7" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E7" s="1">
         <v>5.41</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B8" t="s">
         <v>44</v>
       </c>
-      <c r="B8" t="s">
-        <v>50</v>
-      </c>
       <c r="C8" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E8" s="1">
         <v>17.739999999999998</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B9" t="s">
         <v>44</v>
       </c>
-      <c r="B9" t="s">
-        <v>50</v>
-      </c>
       <c r="C9" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E9" s="1">
         <v>17.739999999999998</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B10" t="s">
         <v>44</v>
       </c>
-      <c r="B10" t="s">
-        <v>50</v>
-      </c>
       <c r="C10" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E10" s="1">
         <v>17.739999999999998</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B11" t="s">
         <v>44</v>
       </c>
-      <c r="B11" t="s">
-        <v>50</v>
-      </c>
       <c r="C11" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E11" s="1">
         <v>17.739999999999998</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B12" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E12" s="1">
         <v>19.53</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B13" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E13" s="1">
         <v>19.53</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B14" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E14" s="1">
         <v>19.53</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B15" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E15" s="1">
         <v>19.53</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B16" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E16" s="1">
         <v>16.18</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B17" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E17" s="1">
         <v>16.18</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B18" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E18" s="1">
         <v>16.18</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B19" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E19" s="1">
         <v>16.18</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
